--- a/forms/trg/Formulir_TRG_natural-drug.xlsx
+++ b/forms/trg/Formulir_TRG_natural-drug.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B30)</f>
+        <f>COUNTA(Anggota!B5:B31)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F30)</f>
+        <f>COUNTA(Anggota!F5:F31)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,22 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Habibie, S.Si., M.Pharm.Sc., PhD., Apt</t>
+          <t>Prof. Subehan, S.Si., M.Pharm.Sc., PhD., Apt</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Univesitas Hasanuddin</t>
+          <t>Universitas Hasanuddin</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Molecular Pharmacology</t>
+          <t>Phytochemicals</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -939,7 +939,7 @@
       <c r="K5" s="12" t="n"/>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57217047207</t>
+          <t>23478515300</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -954,22 +954,22 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof. Andi Dian Permana, S.Si., M.Si., PhD., Apt</t>
+          <t>Habibie, S.Si., M.Pharm.Sc., PhD., Apt</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Universitas Hasanuddin</t>
+          <t>Univesitas Hasanuddin</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Dermal and Trandermal Drug Delivery</t>
+          <t>Molecular Pharmacology</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -980,7 +980,7 @@
       <c r="K6" s="12" t="n"/>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>57208018126</t>
+          <t>57217047207</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -995,12 +995,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Ismail, S.Si., M.Si., Apt</t>
+          <t>Prof. Andi Dian Permana, S.Si., M.Si., PhD., Apt</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Pharmacognosy</t>
+          <t>Dermal and Trandermal Drug Delivery</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1021,7 +1021,7 @@
       <c r="K7" s="12" t="n"/>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>57420405900</t>
+          <t>57208018126</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Yayu Mulsiany Evary, S.Si., M.Pharm.Sci., Apt</t>
+          <t>Ismail, S.Si., M.Si., Apt</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1051,22 +1051,18 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Phytochemistry</t>
+          <t>Pharmacognosy</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-5504-325X</t>
-        </is>
-      </c>
+      <c r="J8" s="12" t="n"/>
       <c r="K8" s="12" t="n"/>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>56938929300</t>
+          <t>57420405900</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1081,22 +1077,22 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Frederika Tangdilintin, S.Si., M.Si., Apt.</t>
+          <t>Yayu Mulsiany Evary, S.Si., M.Pharm.Sci., Apt</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Univesitas Hasanuddin</t>
+          <t>Universitas Hasanuddin</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>pharmaceutical science</t>
+          <t>Phytochemistry</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1105,13 +1101,13 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0009-0008-7579-7110</t>
+          <t>0000-0001-5504-325X</t>
         </is>
       </c>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>58309379500</t>
+          <t>56938929300</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1126,17 +1122,17 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Alghifary Anas Achmad, S.Si., M.Si., Apt.</t>
+          <t>Frederika Tangdilintin, S.Si., M.Si., Apt.</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Universitas Hasanuddin</t>
+          <t>Univesitas Hasanuddin</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -1148,11 +1144,15 @@
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
-      <c r="J10" s="12" t="n"/>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>0009-0008-7579-7110</t>
+        </is>
+      </c>
       <c r="K10" s="12" t="n"/>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>58839187200</t>
+          <t>58309379500</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1167,37 +1167,33 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Prof. Yoshihiro Hayakawa</t>
+          <t>Alghifary Anas Achmad, S.Si., M.Si., Apt.</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>University of Toyama</t>
+          <t>Universitas Hasanuddin</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Immunology, Cancer biology</t>
+          <t>pharmaceutical science</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
-      <c r="J11" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-7921-1171</t>
-        </is>
-      </c>
+      <c r="J11" s="12" t="n"/>
       <c r="K11" s="12" t="n"/>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>57136248400</t>
+          <t>58839187200</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1212,22 +1208,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Besse Hardianti S.Si., M.Pharm.Sc., PhD., Apt</t>
+          <t>Prof. Yoshihiro Hayakawa</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Univesitas Almarisah Madani</t>
+          <t>University of Toyama</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Cancer biology and immunology</t>
+          <t>Immunology, Cancer biology</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1236,13 +1232,13 @@
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-9705-128X</t>
+          <t>0000-0002-7921-1171</t>
         </is>
       </c>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>57212373469</t>
+          <t>57136248400</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1257,31 +1253,39 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Dr.Mandeep Marwah</t>
+          <t>Besse Hardianti S.Si., M.Pharm.Sc., PhD., Apt</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Aston University, United Kingdom</t>
+          <t>Univesitas Almarisah Madani</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Translational Pharmaceutics; Advanced Drug Delivery; Pharmaceutical Formulation; Liposomes; Transdermal Drug Delivery; Microneedles; Targeted and Controlled Drug Delivery; Hydrogen Sulphide-based Therapeutics</t>
+          <t>Cancer biology and immunology</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
       <c r="I13" s="12" t="n"/>
-      <c r="J13" s="12" t="n"/>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-9705-128X</t>
+        </is>
+      </c>
       <c r="K13" s="12" t="n"/>
-      <c r="L13" s="12" t="n"/>
+      <c r="L13" s="11" t="inlineStr">
+        <is>
+          <t>57212373469</t>
+        </is>
+      </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1294,22 +1298,22 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Putri Utami Haris</t>
+          <t>Dr.Mandeep Marwah</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Universitas Hasanuddin</t>
+          <t>Aston University, United Kingdom</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Master Student</t>
+          <t>Translational Pharmaceutics; Advanced Drug Delivery; Pharmaceutical Formulation; Liposomes; Transdermal Drug Delivery; Microneedles; Targeted and Controlled Drug Delivery; Hydrogen Sulphide-based Therapeutics</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -1331,12 +1335,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Nurul Auliya Syahrul</t>
+          <t>Putri Utami Haris</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1368,12 +1372,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Islamiaty Burhanuddin</t>
+          <t>Nurul Auliya Syahrul</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1405,12 +1409,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Andi Muhammad Indra Ashary Assir</t>
+          <t>Islamiaty Burhanuddin</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1442,22 +1446,22 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Darwis</t>
+          <t>Andi Muhammad Indra Ashary Assir</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
+          <t>Universitas Hasanuddin</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
           <t>Master Student</t>
-        </is>
-      </c>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>NATURE-DRUG Team</t>
         </is>
       </c>
       <c r="F18" s="12" t="n"/>
@@ -1477,10 +1481,26 @@
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="11" t="n"/>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Darwis</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Master Student</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>NATURE-DRUG Team</t>
+        </is>
+      </c>
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="12" t="n"/>
       <c r="H19" s="12" t="n"/>
@@ -1488,7 +1508,11 @@
       <c r="J19" s="12" t="n"/>
       <c r="K19" s="12" t="n"/>
       <c r="L19" s="12" t="n"/>
-      <c r="M19" s="12" t="n"/>
+      <c r="M19" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1677,15 +1701,32 @@
       <c r="L30" s="12" t="n"/>
       <c r="M30" s="12" t="n"/>
     </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="12" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="12" t="n"/>
+      <c r="G31" s="12" t="n"/>
+      <c r="H31" s="12" t="n"/>
+      <c r="I31" s="12" t="n"/>
+      <c r="J31" s="12" t="n"/>
+      <c r="K31" s="12" t="n"/>
+      <c r="L31" s="12" t="n"/>
+      <c r="M31" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
